--- a/optaplanner-examples/data/meetingscheduling/unsolved/50meetings-160timegrains-5rooms.xlsx
+++ b/optaplanner-examples/data/meetingscheduling/unsolved/50meetings-160timegrains-5rooms.xlsx
@@ -7,10 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="Configuration" r:id="rId3" sheetId="1"/>
-    <sheet name="Persons" r:id="rId4" sheetId="2"/>
-    <sheet name="Meetings" r:id="rId5" sheetId="3"/>
-    <sheet name="Days" r:id="rId6" sheetId="4"/>
-    <sheet name="Rooms" r:id="rId7" sheetId="5"/>
+    <sheet name="Days" r:id="rId4" sheetId="2"/>
+    <sheet name="Rooms" r:id="rId5" sheetId="3"/>
+    <sheet name="Persons" r:id="rId6" sheetId="4"/>
+    <sheet name="Meetings" r:id="rId7" sheetId="5"/>
     <sheet name="Rooms view" r:id="rId8" sheetId="6"/>
     <sheet name="Persons view" r:id="rId9" sheetId="7"/>
     <sheet name="Printed form view" r:id="rId10" sheetId="8"/>
@@ -19,9 +19,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14899" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15052" uniqueCount="342">
   <si>
-    <t>Thu 2018-07-05 09:42</t>
+    <t>Fri 2018-10-05 13:50</t>
   </si>
   <si>
     <t>Constraint</t>
@@ -69,7 +69,64 @@
     <t>Assign larger rooms first</t>
   </si>
   <si>
-    <t>Room Stability</t>
+    <t>Room stability</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>Lunch hour start time</t>
+  </si>
+  <si>
+    <t>Mon 2018-01-01</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>Tue 2018-01-02</t>
+  </si>
+  <si>
+    <t>Wed 2018-01-03</t>
+  </si>
+  <si>
+    <t>Thu 2018-01-04</t>
+  </si>
+  <si>
+    <t>Fri 2018-01-05</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>R 1</t>
+  </si>
+  <si>
+    <t>R 2</t>
+  </si>
+  <si>
+    <t>R 3</t>
+  </si>
+  <si>
+    <t>R 4</t>
+  </si>
+  <si>
+    <t>R 5</t>
   </si>
   <si>
     <t>Full name</t>
@@ -214,6 +271,12 @@
   </si>
   <si>
     <t>Preferred attendance list</t>
+  </si>
+  <si>
+    <t>Starting time</t>
+  </si>
+  <si>
+    <t>Room</t>
   </si>
   <si>
     <t>Strategize B2B</t>
@@ -625,66 +688,6 @@
   </si>
   <si>
     <t>Ivy Cole, Chad Li, Beth Green, Chad King, Hugo Watt</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>End</t>
-  </si>
-  <si>
-    <t>Lunch hour start time</t>
-  </si>
-  <si>
-    <t>Mon 2018-01-01</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>Tue 2018-01-02</t>
-  </si>
-  <si>
-    <t>Wed 2018-01-03</t>
-  </si>
-  <si>
-    <t>Thu 2018-01-04</t>
-  </si>
-  <si>
-    <t>Fri 2018-01-05</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Capacity</t>
-  </si>
-  <si>
-    <t>R 1</t>
-  </si>
-  <si>
-    <t>R 2</t>
-  </si>
-  <si>
-    <t>R 3</t>
-  </si>
-  <si>
-    <t>R 4</t>
-  </si>
-  <si>
-    <t>R 5</t>
-  </si>
-  <si>
-    <t>Room</t>
   </si>
   <si>
     <t>08:15</t>
@@ -1175,12 +1178,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="60.33203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="8.57421875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.04296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="53.4453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="7.68359375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.515625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1342,215 +1345,97 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.9453125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.0078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="6.0859375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="6.0859375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="20.734375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="s">
-        <v>57</v>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1561,7 +1446,289 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="6.48828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="8.8359375" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -1571,34 +1738,46 @@
     <col min="5" max="5" width="19.53125" customWidth="true"/>
     <col min="6" max="6" width="19.53125" customWidth="true"/>
     <col min="7" max="7" width="19.53125" customWidth="true"/>
+    <col min="8" max="8" width="19.53125" customWidth="true"/>
+    <col min="9" max="9" width="19.53125" customWidth="true"/>
+    <col min="10" max="10" width="19.53125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>83</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -1613,15 +1792,24 @@
         <v>5</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -1636,15 +1824,24 @@
         <v>5</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -1659,15 +1856,24 @@
         <v>5</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>21</v>
+        <v>40</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -1682,15 +1888,24 @@
         <v>5</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>75</v>
+        <v>96</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -1705,15 +1920,24 @@
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -1728,15 +1952,24 @@
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>80</v>
+        <v>101</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
@@ -1751,15 +1984,24 @@
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
@@ -1774,15 +2016,24 @@
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
@@ -1797,15 +2048,24 @@
         <v>5</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>88</v>
+        <v>109</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
@@ -1820,15 +2080,24 @@
         <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>91</v>
+        <v>112</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
@@ -1843,15 +2112,24 @@
         <v>5</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
@@ -1866,15 +2144,24 @@
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>96</v>
+        <v>117</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -1889,15 +2176,24 @@
         <v>5</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>99</v>
+        <v>120</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
@@ -1912,15 +2208,24 @@
         <v>5</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>102</v>
+        <v>123</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
@@ -1935,15 +2240,24 @@
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>105</v>
+        <v>126</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
@@ -1958,15 +2272,24 @@
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>108</v>
+        <v>129</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>5</v>
@@ -1981,15 +2304,24 @@
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>132</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>5</v>
@@ -2004,15 +2336,24 @@
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>114</v>
+        <v>135</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>5</v>
@@ -2027,15 +2368,24 @@
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>23</v>
+        <v>42</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>5</v>
@@ -2050,15 +2400,24 @@
         <v>5</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>119</v>
+        <v>140</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>5</v>
@@ -2073,15 +2432,24 @@
         <v>5</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>122</v>
+        <v>143</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>5</v>
@@ -2096,15 +2464,24 @@
         <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>125</v>
+        <v>146</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>5</v>
@@ -2119,15 +2496,24 @@
         <v>5</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>128</v>
+        <v>149</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>5</v>
@@ -2142,15 +2528,24 @@
         <v>5</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>5</v>
@@ -2165,15 +2560,24 @@
         <v>5</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>133</v>
+        <v>154</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>5</v>
@@ -2188,15 +2592,24 @@
         <v>5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>136</v>
+        <v>157</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>5</v>
@@ -2211,15 +2624,24 @@
         <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>45</v>
+        <v>64</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>5</v>
@@ -2234,15 +2656,24 @@
         <v>5</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>141</v>
+        <v>162</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>5</v>
@@ -2257,15 +2688,24 @@
         <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="G30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>5</v>
@@ -2280,15 +2720,24 @@
         <v>5</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>146</v>
+        <v>167</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>5</v>
@@ -2303,15 +2752,24 @@
         <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>149</v>
+        <v>170</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>5</v>
@@ -2326,15 +2784,24 @@
         <v>5</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>152</v>
+        <v>173</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>5</v>
@@ -2349,15 +2816,24 @@
         <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>155</v>
+        <v>176</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>5</v>
@@ -2372,15 +2848,24 @@
         <v>5</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>158</v>
+        <v>179</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>5</v>
@@ -2395,15 +2880,24 @@
         <v>5</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>161</v>
+        <v>182</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>5</v>
@@ -2418,15 +2912,24 @@
         <v>5</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>164</v>
+        <v>185</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>5</v>
@@ -2441,15 +2944,24 @@
         <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="G38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J38" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>5</v>
@@ -2464,15 +2976,24 @@
         <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="G39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J39" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>5</v>
@@ -2487,15 +3008,24 @@
         <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>171</v>
+        <v>192</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>5</v>
@@ -2510,15 +3040,24 @@
         <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>174</v>
+        <v>195</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>5</v>
@@ -2533,15 +3072,24 @@
         <v>5</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>177</v>
+        <v>198</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>5</v>
@@ -2556,15 +3104,24 @@
         <v>5</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>5</v>
@@ -2579,15 +3136,24 @@
         <v>5</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>183</v>
+        <v>204</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>5</v>
@@ -2602,15 +3168,24 @@
         <v>5</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>186</v>
+        <v>207</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>5</v>
@@ -2625,15 +3200,24 @@
         <v>5</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="G46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>5</v>
@@ -2648,15 +3232,24 @@
         <v>5</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>191</v>
+        <v>212</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>5</v>
@@ -2671,15 +3264,24 @@
         <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="G48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>5</v>
@@ -2694,15 +3296,24 @@
         <v>5</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>196</v>
+        <v>217</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>5</v>
@@ -2717,15 +3328,24 @@
         <v>5</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>199</v>
+        <v>220</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>5</v>
@@ -2740,174 +3360,19 @@
         <v>5</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="16.3828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="6.3984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="6.32421875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="23.6875" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="7.109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="10.10546875" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>16.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>12.0</v>
+      <c r="H51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2921,170 +3386,170 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:FF7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="7.02734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="52" max="52" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="53" max="53" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="54" max="54" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="55" max="55" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="56" max="56" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="57" max="57" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="58" max="58" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="59" max="59" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="60" max="60" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="61" max="61" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="62" max="62" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="63" max="63" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="64" max="64" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="65" max="65" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="66" max="66" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="67" max="67" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="68" max="68" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="69" max="69" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="70" max="70" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="71" max="71" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="72" max="72" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="73" max="73" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="74" max="74" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="75" max="75" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="76" max="76" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="77" max="77" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="78" max="78" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="79" max="79" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="80" max="80" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="81" max="81" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="82" max="82" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="83" max="83" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="84" max="84" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="85" max="85" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="86" max="86" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="87" max="87" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="88" max="88" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="89" max="89" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="90" max="90" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="91" max="91" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="92" max="92" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="93" max="93" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="94" max="94" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="95" max="95" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="96" max="96" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="97" max="97" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="98" max="98" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="99" max="99" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="100" max="100" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="101" max="101" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="102" max="102" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="103" max="103" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="104" max="104" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="105" max="105" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="106" max="106" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="107" max="107" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="108" max="108" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="109" max="109" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="110" max="110" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="111" max="111" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="112" max="112" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="113" max="113" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="114" max="114" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="115" max="115" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="116" max="116" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="117" max="117" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="118" max="118" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="119" max="119" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="120" max="120" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="121" max="121" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="122" max="122" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="123" max="123" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="124" max="124" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="125" max="125" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="126" max="126" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="127" max="127" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="128" max="128" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="129" max="129" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="130" max="130" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="131" max="131" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="132" max="132" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="133" max="133" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="134" max="134" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="135" max="135" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="136" max="136" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="137" max="137" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="138" max="138" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="139" max="139" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="140" max="140" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="141" max="141" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="142" max="142" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="143" max="143" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="144" max="144" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="145" max="145" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="146" max="146" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="147" max="147" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="148" max="148" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="149" max="149" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="150" max="150" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="151" max="151" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="152" max="152" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="153" max="153" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="154" max="154" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="155" max="155" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="156" max="156" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="157" max="157" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="158" max="158" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="159" max="159" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="160" max="160" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="161" max="161" width="7.01953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="6.44921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="32" max="32" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="33" max="33" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="34" max="34" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="35" max="35" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="36" max="36" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="46" max="46" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="47" max="47" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="48" max="48" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="49" max="49" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="50" max="50" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="51" max="51" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="52" max="52" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="53" max="53" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="54" max="54" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="55" max="55" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="56" max="56" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="57" max="57" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="58" max="58" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="59" max="59" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="60" max="60" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="61" max="61" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="62" max="62" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="63" max="63" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="64" max="64" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="65" max="65" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="66" max="66" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="67" max="67" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="68" max="68" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="69" max="69" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="70" max="70" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="71" max="71" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="72" max="72" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="73" max="73" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="74" max="74" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="75" max="75" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="76" max="76" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="77" max="77" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="78" max="78" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="79" max="79" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="80" max="80" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="81" max="81" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="82" max="82" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="83" max="83" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="84" max="84" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="85" max="85" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="86" max="86" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="87" max="87" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="88" max="88" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="89" max="89" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="90" max="90" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="91" max="91" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="92" max="92" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="93" max="93" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="94" max="94" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="95" max="95" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="96" max="96" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="97" max="97" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="98" max="98" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="99" max="99" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="100" max="100" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="101" max="101" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="102" max="102" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="103" max="103" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="104" max="104" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="105" max="105" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="106" max="106" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="107" max="107" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="108" max="108" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="109" max="109" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="110" max="110" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="111" max="111" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="112" max="112" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="113" max="113" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="114" max="114" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="115" max="115" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="116" max="116" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="117" max="117" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="118" max="118" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="119" max="119" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="120" max="120" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="121" max="121" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="122" max="122" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="123" max="123" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="124" max="124" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="125" max="125" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="126" max="126" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="127" max="127" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="128" max="128" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="129" max="129" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="130" max="130" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="131" max="131" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="132" max="132" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="133" max="133" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="134" max="134" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="135" max="135" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="136" max="136" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="137" max="137" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="138" max="138" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="139" max="139" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="140" max="140" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="141" max="141" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="142" max="142" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="143" max="143" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="144" max="144" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="145" max="145" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="146" max="146" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="147" max="147" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="148" max="148" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="149" max="149" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="150" max="150" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="151" max="151" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="152" max="152" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="153" max="153" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="154" max="154" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="155" max="155" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="156" max="156" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="157" max="157" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="158" max="158" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="159" max="159" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="160" max="160" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="161" max="161" width="6.12109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3092,7 +3557,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
@@ -3200,7 +3665,7 @@
         <v>5</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>210</v>
+        <v>25</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>5</v>
@@ -3308,7 +3773,7 @@
         <v>5</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>211</v>
+        <v>26</v>
       </c>
       <c r="BW1" s="1" t="s">
         <v>5</v>
@@ -3416,7 +3881,7 @@
         <v>5</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>212</v>
+        <v>27</v>
       </c>
       <c r="DG1" s="1" t="s">
         <v>5</v>
@@ -3524,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>213</v>
+        <v>28</v>
       </c>
       <c r="EQ1" s="1" t="s">
         <v>5</v>
@@ -3574,492 +4039,492 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>221</v>
+        <v>85</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AM2" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="AU2" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="AW2" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="AX2" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="AY2" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="AZ2" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="BA2" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="BB2" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="BC2" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="BD2" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="BE2" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="BF2" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="BG2" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="BH2" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="BI2" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="BJ2" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="BK2" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="BL2" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="BM2" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="BN2" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="BO2" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="BP2" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="BQ2" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="BR2" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="BS2" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="BT2" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="AL2" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="AN2" s="1" t="s">
+      <c r="BU2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="BV2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="BW2" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="BX2" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="BY2" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="BZ2" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="CA2" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="CB2" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="CC2" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="CD2" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="CE2" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="CF2" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="CG2" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="CH2" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="CI2" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="CJ2" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="CK2" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="CL2" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="CM2" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="CN2" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="CO2" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="CP2" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="CQ2" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="CR2" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="BJ2" s="1" t="s">
+      <c r="CS2" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="CT2" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="BL2" s="1" t="s">
+      <c r="CU2" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="BM2" s="1" t="s">
+      <c r="CV2" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="BN2" s="1" t="s">
+      <c r="CW2" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="BO2" s="1" t="s">
+      <c r="CX2" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="BP2" s="1" t="s">
+      <c r="CY2" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="BQ2" s="1" t="s">
+      <c r="CZ2" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="BR2" s="1" t="s">
+      <c r="DA2" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="BS2" s="1" t="s">
+      <c r="DB2" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="BT2" s="1" t="s">
+      <c r="DC2" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="BU2" s="1" t="s">
+      <c r="DD2" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="BV2" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="BW2" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="BX2" s="1" t="s">
+      <c r="DE2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="DF2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="DG2" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="BY2" s="1" t="s">
+      <c r="DH2" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="BZ2" s="1" t="s">
+      <c r="DI2" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="CA2" s="1" t="s">
+      <c r="DJ2" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="CB2" s="1" t="s">
+      <c r="DK2" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="CC2" s="1" t="s">
+      <c r="DL2" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="CD2" s="1" t="s">
+      <c r="DM2" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="CE2" s="1" t="s">
+      <c r="DN2" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="CF2" s="1" t="s">
+      <c r="DO2" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="CG2" s="1" t="s">
+      <c r="DP2" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="CH2" s="1" t="s">
+      <c r="DQ2" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="CI2" s="1" t="s">
+      <c r="DR2" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="CJ2" s="1" t="s">
+      <c r="DS2" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="CK2" s="1" t="s">
+      <c r="DT2" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="CL2" s="1" t="s">
+      <c r="DU2" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="CM2" s="1" t="s">
+      <c r="DV2" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="CN2" s="1" t="s">
+      <c r="DW2" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="CO2" s="1" t="s">
+      <c r="DX2" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="CP2" s="1" t="s">
+      <c r="DY2" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="CQ2" s="1" t="s">
+      <c r="DZ2" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="CR2" s="1" t="s">
+      <c r="EA2" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="CS2" s="1" t="s">
+      <c r="EB2" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="CT2" s="1" t="s">
+      <c r="EC2" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="CU2" s="1" t="s">
+      <c r="ED2" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="CV2" s="1" t="s">
+      <c r="EE2" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="CW2" s="1" t="s">
+      <c r="EF2" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="CX2" s="1" t="s">
+      <c r="EG2" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="CY2" s="1" t="s">
+      <c r="EH2" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="CZ2" s="1" t="s">
+      <c r="EI2" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="DA2" s="1" t="s">
+      <c r="EJ2" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="DB2" s="1" t="s">
+      <c r="EK2" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="DC2" s="1" t="s">
+      <c r="EL2" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="DD2" s="1" t="s">
+      <c r="EM2" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="DE2" s="1" t="s">
+      <c r="EN2" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="DF2" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="DG2" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="DH2" s="1" t="s">
+      <c r="EO2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="EP2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="EQ2" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="DI2" s="1" t="s">
+      <c r="ER2" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="DJ2" s="1" t="s">
+      <c r="ES2" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="DK2" s="1" t="s">
+      <c r="ET2" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="DL2" s="1" t="s">
+      <c r="EU2" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="DM2" s="1" t="s">
+      <c r="EV2" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="DN2" s="1" t="s">
+      <c r="EW2" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="DO2" s="1" t="s">
+      <c r="EX2" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="DP2" s="1" t="s">
+      <c r="EY2" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="DQ2" s="1" t="s">
+      <c r="EZ2" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="DR2" s="1" t="s">
+      <c r="FA2" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="DS2" s="1" t="s">
+      <c r="FB2" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="DT2" s="1" t="s">
+      <c r="FC2" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="DU2" s="1" t="s">
+      <c r="FD2" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="DV2" s="1" t="s">
+      <c r="FE2" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="DW2" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="DX2" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="DY2" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="DZ2" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="EA2" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="EB2" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="EC2" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="ED2" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="EE2" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="EF2" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="EG2" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="EH2" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="EI2" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="EJ2" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="EK2" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="EL2" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="EM2" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="EN2" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="EO2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="EP2" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="EQ2" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="ER2" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="ES2" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="ET2" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="EU2" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="EV2" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="EW2" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="EX2" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="EY2" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="EZ2" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="FA2" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="FB2" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="FC2" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="FD2" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="FE2" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="3" ht="30.0" customHeight="true">
       <c r="A3" s="2" t="s">
-        <v>216</v>
+        <v>31</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>5</v>
@@ -4544,7 +5009,7 @@
     </row>
     <row r="4" ht="30.0" customHeight="true">
       <c r="A4" s="2" t="s">
-        <v>217</v>
+        <v>32</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>5</v>
@@ -5029,7 +5494,7 @@
     </row>
     <row r="5" ht="30.0" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>218</v>
+        <v>33</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>5</v>
@@ -5514,7 +5979,7 @@
     </row>
     <row r="6" ht="30.0" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>219</v>
+        <v>34</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>5</v>
@@ -5999,7 +6464,7 @@
     </row>
     <row r="7" ht="30.0" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>220</v>
+        <v>35</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>5</v>
@@ -6500,171 +6965,171 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:FG82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="13.08984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="48" max="48" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="49" max="49" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="50" max="50" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="51" max="51" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="52" max="52" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="53" max="53" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="54" max="54" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="55" max="55" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="56" max="56" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="57" max="57" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="58" max="58" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="59" max="59" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="60" max="60" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="61" max="61" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="62" max="62" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="63" max="63" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="64" max="64" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="65" max="65" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="66" max="66" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="67" max="67" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="68" max="68" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="69" max="69" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="70" max="70" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="71" max="71" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="72" max="72" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="73" max="73" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="74" max="74" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="75" max="75" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="76" max="76" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="77" max="77" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="78" max="78" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="79" max="79" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="80" max="80" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="81" max="81" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="82" max="82" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="83" max="83" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="84" max="84" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="85" max="85" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="86" max="86" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="87" max="87" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="88" max="88" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="89" max="89" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="90" max="90" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="91" max="91" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="92" max="92" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="93" max="93" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="94" max="94" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="95" max="95" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="96" max="96" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="97" max="97" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="98" max="98" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="99" max="99" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="100" max="100" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="101" max="101" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="102" max="102" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="103" max="103" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="104" max="104" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="105" max="105" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="106" max="106" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="107" max="107" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="108" max="108" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="109" max="109" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="110" max="110" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="111" max="111" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="112" max="112" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="113" max="113" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="114" max="114" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="115" max="115" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="116" max="116" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="117" max="117" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="118" max="118" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="119" max="119" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="120" max="120" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="121" max="121" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="122" max="122" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="123" max="123" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="124" max="124" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="125" max="125" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="126" max="126" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="127" max="127" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="128" max="128" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="129" max="129" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="130" max="130" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="131" max="131" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="132" max="132" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="133" max="133" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="134" max="134" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="135" max="135" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="136" max="136" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="137" max="137" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="138" max="138" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="139" max="139" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="140" max="140" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="141" max="141" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="142" max="142" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="143" max="143" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="144" max="144" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="145" max="145" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="146" max="146" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="147" max="147" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="148" max="148" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="149" max="149" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="150" max="150" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="151" max="151" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="152" max="152" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="153" max="153" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="154" max="154" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="155" max="155" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="156" max="156" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="157" max="157" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="158" max="158" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="159" max="159" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="160" max="160" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="161" max="161" width="7.01953125" customWidth="true" bestFit="true"/>
-    <col min="162" max="162" width="7.01953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="7.35546875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.67578125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="16" max="16" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="17" max="17" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="18" max="18" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="19" max="19" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="32" max="32" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="33" max="33" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="34" max="34" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="35" max="35" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="36" max="36" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="46" max="46" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="47" max="47" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="48" max="48" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="49" max="49" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="50" max="50" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="51" max="51" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="52" max="52" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="53" max="53" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="54" max="54" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="55" max="55" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="56" max="56" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="57" max="57" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="58" max="58" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="59" max="59" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="60" max="60" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="61" max="61" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="62" max="62" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="63" max="63" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="64" max="64" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="65" max="65" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="66" max="66" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="67" max="67" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="68" max="68" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="69" max="69" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="70" max="70" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="71" max="71" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="72" max="72" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="73" max="73" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="74" max="74" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="75" max="75" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="76" max="76" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="77" max="77" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="78" max="78" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="79" max="79" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="80" max="80" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="81" max="81" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="82" max="82" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="83" max="83" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="84" max="84" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="85" max="85" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="86" max="86" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="87" max="87" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="88" max="88" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="89" max="89" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="90" max="90" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="91" max="91" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="92" max="92" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="93" max="93" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="94" max="94" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="95" max="95" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="96" max="96" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="97" max="97" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="98" max="98" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="99" max="99" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="100" max="100" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="101" max="101" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="102" max="102" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="103" max="103" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="104" max="104" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="105" max="105" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="106" max="106" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="107" max="107" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="108" max="108" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="109" max="109" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="110" max="110" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="111" max="111" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="112" max="112" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="113" max="113" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="114" max="114" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="115" max="115" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="116" max="116" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="117" max="117" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="118" max="118" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="119" max="119" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="120" max="120" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="121" max="121" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="122" max="122" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="123" max="123" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="124" max="124" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="125" max="125" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="126" max="126" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="127" max="127" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="128" max="128" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="129" max="129" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="130" max="130" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="131" max="131" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="132" max="132" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="133" max="133" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="134" max="134" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="135" max="135" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="136" max="136" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="137" max="137" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="138" max="138" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="139" max="139" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="140" max="140" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="141" max="141" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="142" max="142" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="143" max="143" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="144" max="144" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="145" max="145" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="146" max="146" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="147" max="147" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="148" max="148" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="149" max="149" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="150" max="150" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="151" max="151" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="152" max="152" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="153" max="153" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="154" max="154" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="155" max="155" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="156" max="156" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="157" max="157" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="158" max="158" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="159" max="159" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="160" max="160" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="161" max="161" width="6.12109375" customWidth="true" bestFit="true"/>
+    <col min="162" max="162" width="6.12109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6675,7 +7140,7 @@
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
@@ -6783,7 +7248,7 @@
         <v>5</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>210</v>
+        <v>25</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>5</v>
@@ -6891,7 +7356,7 @@
         <v>5</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>211</v>
+        <v>26</v>
       </c>
       <c r="BX1" s="1" t="s">
         <v>5</v>
@@ -6999,7 +7464,7 @@
         <v>5</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>212</v>
+        <v>27</v>
       </c>
       <c r="DH1" s="1" t="s">
         <v>5</v>
@@ -7107,7 +7572,7 @@
         <v>5</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>213</v>
+        <v>28</v>
       </c>
       <c r="ER1" s="1" t="s">
         <v>5</v>
@@ -7157,498 +7622,498 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AL2" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN2" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="AU2" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="AW2" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="AX2" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="AY2" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="AZ2" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="BA2" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="BB2" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="BC2" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="BD2" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="BE2" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="BF2" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="BG2" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="BH2" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="BI2" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="BJ2" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="BK2" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="BL2" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="BM2" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="BN2" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="BO2" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="BP2" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="BQ2" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="BR2" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="BS2" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="BT2" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="BU2" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="AM2" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="AO2" s="1" t="s">
+      <c r="BV2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="BW2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="BX2" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="BY2" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="BZ2" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="CA2" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="CB2" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="CC2" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="CD2" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="CE2" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="CF2" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="CG2" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="CH2" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="CI2" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="CJ2" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="CK2" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="CL2" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="CM2" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="CN2" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="CO2" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="CP2" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="CQ2" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="CR2" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="BJ2" s="1" t="s">
+      <c r="CS2" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="CT2" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="BL2" s="1" t="s">
+      <c r="CU2" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="BM2" s="1" t="s">
+      <c r="CV2" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="BN2" s="1" t="s">
+      <c r="CW2" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="BO2" s="1" t="s">
+      <c r="CX2" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="BP2" s="1" t="s">
+      <c r="CY2" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="BQ2" s="1" t="s">
+      <c r="CZ2" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="BR2" s="1" t="s">
+      <c r="DA2" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="BS2" s="1" t="s">
+      <c r="DB2" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="BT2" s="1" t="s">
+      <c r="DC2" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="BU2" s="1" t="s">
+      <c r="DD2" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="BV2" s="1" t="s">
+      <c r="DE2" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="BW2" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="BX2" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="BY2" s="1" t="s">
+      <c r="DF2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="DG2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="DH2" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="BZ2" s="1" t="s">
+      <c r="DI2" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="CA2" s="1" t="s">
+      <c r="DJ2" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="CB2" s="1" t="s">
+      <c r="DK2" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="CC2" s="1" t="s">
+      <c r="DL2" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="CD2" s="1" t="s">
+      <c r="DM2" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="CE2" s="1" t="s">
+      <c r="DN2" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="CF2" s="1" t="s">
+      <c r="DO2" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="CG2" s="1" t="s">
+      <c r="DP2" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="CH2" s="1" t="s">
+      <c r="DQ2" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="CI2" s="1" t="s">
+      <c r="DR2" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="CJ2" s="1" t="s">
+      <c r="DS2" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="CK2" s="1" t="s">
+      <c r="DT2" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="CL2" s="1" t="s">
+      <c r="DU2" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="CM2" s="1" t="s">
+      <c r="DV2" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="CN2" s="1" t="s">
+      <c r="DW2" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="CO2" s="1" t="s">
+      <c r="DX2" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="CP2" s="1" t="s">
+      <c r="DY2" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="CQ2" s="1" t="s">
+      <c r="DZ2" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="CR2" s="1" t="s">
+      <c r="EA2" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="CS2" s="1" t="s">
+      <c r="EB2" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="CT2" s="1" t="s">
+      <c r="EC2" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="CU2" s="1" t="s">
+      <c r="ED2" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="CV2" s="1" t="s">
+      <c r="EE2" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="CW2" s="1" t="s">
+      <c r="EF2" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="CX2" s="1" t="s">
+      <c r="EG2" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="CY2" s="1" t="s">
+      <c r="EH2" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="CZ2" s="1" t="s">
+      <c r="EI2" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="DA2" s="1" t="s">
+      <c r="EJ2" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="DB2" s="1" t="s">
+      <c r="EK2" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="DC2" s="1" t="s">
+      <c r="EL2" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="DD2" s="1" t="s">
+      <c r="EM2" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="DE2" s="1" t="s">
+      <c r="EN2" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="DF2" s="1" t="s">
+      <c r="EO2" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="DG2" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="DH2" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="DI2" s="1" t="s">
+      <c r="EP2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="EQ2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="ER2" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="DJ2" s="1" t="s">
+      <c r="ES2" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="DK2" s="1" t="s">
+      <c r="ET2" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="DL2" s="1" t="s">
+      <c r="EU2" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="DM2" s="1" t="s">
+      <c r="EV2" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="DN2" s="1" t="s">
+      <c r="EW2" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="DO2" s="1" t="s">
+      <c r="EX2" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="DP2" s="1" t="s">
+      <c r="EY2" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="DQ2" s="1" t="s">
+      <c r="EZ2" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="DR2" s="1" t="s">
+      <c r="FA2" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="DS2" s="1" t="s">
+      <c r="FB2" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="DT2" s="1" t="s">
+      <c r="FC2" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="DU2" s="1" t="s">
+      <c r="FD2" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="DV2" s="1" t="s">
+      <c r="FE2" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="DW2" s="1" t="s">
+      <c r="FF2" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="DX2" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="DY2" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="DZ2" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="EA2" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="EB2" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="EC2" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="ED2" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="EE2" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="EF2" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="EG2" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="EH2" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="EI2" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="EJ2" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="EK2" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="EL2" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="EM2" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="EN2" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="EO2" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="EP2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="EQ2" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="ER2" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="ES2" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="ET2" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="EU2" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="EV2" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="EW2" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="EX2" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="EY2" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="EZ2" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="FA2" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="FB2" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="FC2" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="FD2" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="FE2" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="FF2" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="3" ht="30.0" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>5</v>
@@ -8133,10 +8598,10 @@
     </row>
     <row r="4" ht="30.0" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>5</v>
@@ -8621,10 +9086,10 @@
     </row>
     <row r="5" ht="30.0" customHeight="true">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>5</v>
@@ -9109,10 +9574,10 @@
     </row>
     <row r="6" ht="30.0" customHeight="true">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>5</v>
@@ -9597,10 +10062,10 @@
     </row>
     <row r="7" ht="30.0" customHeight="true">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>5</v>
@@ -10085,10 +10550,10 @@
     </row>
     <row r="8" ht="30.0" customHeight="true">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>5</v>
@@ -10573,10 +11038,10 @@
     </row>
     <row r="9" ht="30.0" customHeight="true">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>5</v>
@@ -11061,10 +11526,10 @@
     </row>
     <row r="10" ht="30.0" customHeight="true">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>5</v>
@@ -11549,10 +12014,10 @@
     </row>
     <row r="11" ht="30.0" customHeight="true">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>5</v>
@@ -12037,10 +12502,10 @@
     </row>
     <row r="12" ht="30.0" customHeight="true">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>5</v>
@@ -12525,10 +12990,10 @@
     </row>
     <row r="13" ht="30.0" customHeight="true">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>5</v>
@@ -13013,10 +13478,10 @@
     </row>
     <row r="14" ht="30.0" customHeight="true">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>5</v>
@@ -13501,10 +13966,10 @@
     </row>
     <row r="15" ht="30.0" customHeight="true">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>5</v>
@@ -13989,10 +14454,10 @@
     </row>
     <row r="16" ht="30.0" customHeight="true">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>5</v>
@@ -14477,10 +14942,10 @@
     </row>
     <row r="17" ht="30.0" customHeight="true">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>5</v>
@@ -14965,10 +15430,10 @@
     </row>
     <row r="18" ht="30.0" customHeight="true">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>5</v>
@@ -15453,10 +15918,10 @@
     </row>
     <row r="19" ht="30.0" customHeight="true">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>5</v>
@@ -15941,10 +16406,10 @@
     </row>
     <row r="20" ht="30.0" customHeight="true">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>5</v>
@@ -16429,10 +16894,10 @@
     </row>
     <row r="21" ht="30.0" customHeight="true">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>5</v>
@@ -16917,10 +17382,10 @@
     </row>
     <row r="22" ht="30.0" customHeight="true">
       <c r="A22" s="1" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>5</v>
@@ -17405,10 +17870,10 @@
     </row>
     <row r="23" ht="30.0" customHeight="true">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>5</v>
@@ -17893,10 +18358,10 @@
     </row>
     <row r="24" ht="30.0" customHeight="true">
       <c r="A24" s="1" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>5</v>
@@ -18381,10 +18846,10 @@
     </row>
     <row r="25" ht="30.0" customHeight="true">
       <c r="A25" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>5</v>
@@ -18869,10 +19334,10 @@
     </row>
     <row r="26" ht="30.0" customHeight="true">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>5</v>
@@ -19357,10 +19822,10 @@
     </row>
     <row r="27" ht="30.0" customHeight="true">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>5</v>
@@ -19845,10 +20310,10 @@
     </row>
     <row r="28" ht="30.0" customHeight="true">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>5</v>
@@ -20333,10 +20798,10 @@
     </row>
     <row r="29" ht="30.0" customHeight="true">
       <c r="A29" s="1" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>5</v>
@@ -20821,10 +21286,10 @@
     </row>
     <row r="30" ht="30.0" customHeight="true">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>5</v>
@@ -21309,10 +21774,10 @@
     </row>
     <row r="31" ht="30.0" customHeight="true">
       <c r="A31" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>5</v>
@@ -21797,10 +22262,10 @@
     </row>
     <row r="32" ht="30.0" customHeight="true">
       <c r="A32" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>5</v>
@@ -22285,10 +22750,10 @@
     </row>
     <row r="33" ht="30.0" customHeight="true">
       <c r="A33" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>5</v>
@@ -22773,10 +23238,10 @@
     </row>
     <row r="34" ht="30.0" customHeight="true">
       <c r="A34" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>5</v>
@@ -23261,10 +23726,10 @@
     </row>
     <row r="35" ht="30.0" customHeight="true">
       <c r="A35" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>5</v>
@@ -23749,10 +24214,10 @@
     </row>
     <row r="36" ht="30.0" customHeight="true">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>5</v>
@@ -24237,10 +24702,10 @@
     </row>
     <row r="37" ht="30.0" customHeight="true">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>5</v>
@@ -24725,10 +25190,10 @@
     </row>
     <row r="38" ht="30.0" customHeight="true">
       <c r="A38" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>5</v>
@@ -25213,10 +25678,10 @@
     </row>
     <row r="39" ht="30.0" customHeight="true">
       <c r="A39" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>5</v>
@@ -25701,10 +26166,10 @@
     </row>
     <row r="40" ht="30.0" customHeight="true">
       <c r="A40" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>5</v>
@@ -26189,10 +26654,10 @@
     </row>
     <row r="41" ht="30.0" customHeight="true">
       <c r="A41" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>5</v>
@@ -26677,10 +27142,10 @@
     </row>
     <row r="42" ht="30.0" customHeight="true">
       <c r="A42" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>5</v>
@@ -27165,10 +27630,10 @@
     </row>
     <row r="43" ht="30.0" customHeight="true">
       <c r="A43" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>5</v>
@@ -27653,10 +28118,10 @@
     </row>
     <row r="44" ht="30.0" customHeight="true">
       <c r="A44" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>5</v>
@@ -28141,10 +28606,10 @@
     </row>
     <row r="45" ht="30.0" customHeight="true">
       <c r="A45" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>5</v>
@@ -28629,10 +29094,10 @@
     </row>
     <row r="46" ht="30.0" customHeight="true">
       <c r="A46" s="1" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>5</v>
@@ -29117,10 +29582,10 @@
     </row>
     <row r="47" ht="30.0" customHeight="true">
       <c r="A47" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>5</v>
@@ -29605,10 +30070,10 @@
     </row>
     <row r="48" ht="30.0" customHeight="true">
       <c r="A48" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>5</v>
@@ -30093,10 +30558,10 @@
     </row>
     <row r="49" ht="30.0" customHeight="true">
       <c r="A49" s="1" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>5</v>
@@ -30581,10 +31046,10 @@
     </row>
     <row r="50" ht="30.0" customHeight="true">
       <c r="A50" s="1" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>5</v>
@@ -31069,10 +31534,10 @@
     </row>
     <row r="51" ht="30.0" customHeight="true">
       <c r="A51" s="1" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>5</v>
@@ -31557,10 +32022,10 @@
     </row>
     <row r="52" ht="30.0" customHeight="true">
       <c r="A52" s="1" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>5</v>
@@ -32045,10 +32510,10 @@
     </row>
     <row r="53" ht="30.0" customHeight="true">
       <c r="A53" s="1" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>5</v>
@@ -32533,10 +32998,10 @@
     </row>
     <row r="54" ht="30.0" customHeight="true">
       <c r="A54" s="1" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>5</v>
@@ -33021,10 +33486,10 @@
     </row>
     <row r="55" ht="30.0" customHeight="true">
       <c r="A55" s="1" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>5</v>
@@ -33509,10 +33974,10 @@
     </row>
     <row r="56" ht="30.0" customHeight="true">
       <c r="A56" s="1" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>5</v>
@@ -33997,10 +34462,10 @@
     </row>
     <row r="57" ht="30.0" customHeight="true">
       <c r="A57" s="1" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>5</v>
@@ -34485,10 +34950,10 @@
     </row>
     <row r="58" ht="30.0" customHeight="true">
       <c r="A58" s="1" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>5</v>
@@ -34973,10 +35438,10 @@
     </row>
     <row r="59" ht="30.0" customHeight="true">
       <c r="A59" s="1" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>5</v>
@@ -35461,10 +35926,10 @@
     </row>
     <row r="60" ht="30.0" customHeight="true">
       <c r="A60" s="1" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>5</v>
@@ -35949,10 +36414,10 @@
     </row>
     <row r="61" ht="30.0" customHeight="true">
       <c r="A61" s="1" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>5</v>
@@ -36437,10 +36902,10 @@
     </row>
     <row r="62" ht="30.0" customHeight="true">
       <c r="A62" s="1" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>5</v>
@@ -36925,10 +37390,10 @@
     </row>
     <row r="63" ht="30.0" customHeight="true">
       <c r="A63" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>5</v>
@@ -37413,10 +37878,10 @@
     </row>
     <row r="64" ht="30.0" customHeight="true">
       <c r="A64" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>5</v>
@@ -37901,10 +38366,10 @@
     </row>
     <row r="65" ht="30.0" customHeight="true">
       <c r="A65" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>5</v>
@@ -38389,10 +38854,10 @@
     </row>
     <row r="66" ht="30.0" customHeight="true">
       <c r="A66" s="1" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>5</v>
@@ -38877,10 +39342,10 @@
     </row>
     <row r="67" ht="30.0" customHeight="true">
       <c r="A67" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>5</v>
@@ -39365,10 +39830,10 @@
     </row>
     <row r="68" ht="30.0" customHeight="true">
       <c r="A68" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>5</v>
@@ -39853,10 +40318,10 @@
     </row>
     <row r="69" ht="30.0" customHeight="true">
       <c r="A69" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>5</v>
@@ -40341,10 +40806,10 @@
     </row>
     <row r="70" ht="30.0" customHeight="true">
       <c r="A70" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>5</v>
@@ -40829,10 +41294,10 @@
     </row>
     <row r="71" ht="30.0" customHeight="true">
       <c r="A71" s="1" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>5</v>
@@ -41317,10 +41782,10 @@
     </row>
     <row r="72" ht="30.0" customHeight="true">
       <c r="A72" s="1" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>5</v>
@@ -41805,10 +42270,10 @@
     </row>
     <row r="73" ht="30.0" customHeight="true">
       <c r="A73" s="1" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>5</v>
@@ -42293,10 +42758,10 @@
     </row>
     <row r="74" ht="30.0" customHeight="true">
       <c r="A74" s="1" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>5</v>
@@ -42781,10 +43246,10 @@
     </row>
     <row r="75" ht="30.0" customHeight="true">
       <c r="A75" s="1" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>5</v>
@@ -43269,10 +43734,10 @@
     </row>
     <row r="76" ht="30.0" customHeight="true">
       <c r="A76" s="1" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>5</v>
@@ -43757,10 +44222,10 @@
     </row>
     <row r="77" ht="30.0" customHeight="true">
       <c r="A77" s="1" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>5</v>
@@ -44245,10 +44710,10 @@
     </row>
     <row r="78" ht="30.0" customHeight="true">
       <c r="A78" s="1" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>5</v>
@@ -44733,10 +45198,10 @@
     </row>
     <row r="79" ht="30.0" customHeight="true">
       <c r="A79" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>5</v>
@@ -45221,10 +45686,10 @@
     </row>
     <row r="80" ht="30.0" customHeight="true">
       <c r="A80" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>5</v>
@@ -45709,10 +46174,10 @@
     </row>
     <row r="81" ht="30.0" customHeight="true">
       <c r="A81" s="1" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>5</v>
@@ -46197,10 +46662,10 @@
     </row>
     <row r="82" ht="30.0" customHeight="true">
       <c r="A82" s="1" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>5</v>
@@ -46741,7 +47206,7 @@
   <sheetPr>
     <tabColor rgb="FCE94F"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:B161"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="23.4375" customWidth="true"/>
@@ -46754,481 +47219,481 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5"/>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7"/>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21"/>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25"/>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27"/>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29"/>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31"/>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33"/>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35"/>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="37"/>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39"/>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41"/>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="43"/>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="45"/>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47"/>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="49"/>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51"/>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="53"/>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="55"/>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="57"/>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="59"/>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="61"/>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63"/>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65"/>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="67"/>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="69"/>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="71"/>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="73"/>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="75"/>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="77"/>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="79"/>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="81"/>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="83"/>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="85"/>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="87"/>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="89"/>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="91"/>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="93"/>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="95"/>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="97"/>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="99"/>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="101"/>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="103"/>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="105"/>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="107"/>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="109"/>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="111"/>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="113"/>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="115"/>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="117"/>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="119"/>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="121"/>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="123"/>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="125"/>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="127"/>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="129"/>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="131"/>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="133"/>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="135"/>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="137"/>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="139"/>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="141"/>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="143"/>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="145"/>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="147"/>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="149"/>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="151"/>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="153"/>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="155"/>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="157"/>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="159"/>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="161"/>

--- a/optaplanner-examples/data/meetingscheduling/unsolved/50meetings-160timegrains-5rooms.xlsx
+++ b/optaplanner-examples/data/meetingscheduling/unsolved/50meetings-160timegrains-5rooms.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15052" uniqueCount="342">
   <si>
-    <t>Fri 2018-10-05 13:50</t>
+    <t>Wed 2018-10-10 16:04</t>
   </si>
   <si>
     <t>Constraint</t>
@@ -1066,7 +1066,7 @@
       <b val="true"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1101,6 +1101,11 @@
         <fgColor rgb="FCAF3E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1114,7 +1119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true">
       <alignment wrapText="true" vertical="center"/>
@@ -1138,6 +1143,9 @@
       <alignment wrapText="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true">
       <alignment wrapText="true" vertical="center"/>
     </xf>
   </cellXfs>

--- a/optaplanner-examples/data/meetingscheduling/unsolved/50meetings-160timegrains-5rooms.xlsx
+++ b/optaplanner-examples/data/meetingscheduling/unsolved/50meetings-160timegrains-5rooms.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15052" uniqueCount="342">
   <si>
-    <t>Wed 2018-10-10 16:04</t>
+    <t>Mon 2018-10-15 17:45</t>
   </si>
   <si>
     <t>Constraint</t>
